--- a/docs/publications/close-2025/timesheet-report.xlsx
+++ b/docs/publications/close-2025/timesheet-report.xlsx
@@ -538,14 +538,14 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>CERTIFIED — Tom Metzinger, 15 Sep 2026.</t>
+          <t>REHEARSAL — NOT CERTIFIED. A drive produced this signature to prove the mechanism; no person gave it.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>The signature records what was unfinished when it was given, and those steps are part of it: The paper behind the judgments, The position on each invoice.</t>
+          <t>Nothing resting on it may be sent to a sponsor. The rate itself is arithmetic and stands; what is missing is somebody putting their name to it.</t>
         </is>
       </c>
     </row>
